--- a/Engineering_and_Inverse_Analysis/typical_cloudy_day.xlsx
+++ b/Engineering_and_Inverse_Analysis/typical_cloudy_day.xlsx
@@ -31,31 +31,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>购电功率</t>
+    <t>grid_purchase_kw</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>电化学储能放电</t>
+    <t>battery_discharge_kw</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>燃料电池放电</t>
+    <t>fuel_cell_kw</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>制氢功率</t>
+    <t>electrolyzer_kw</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>充电桩负荷</t>
+    <t>ev_charging_load_kw</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>直流和站用负荷</t>
+    <t>dc_station_load_kw</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>电化学储能充电</t>
+    <t>battery_charge_kw</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -79,13 +79,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -93,7 +93,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -125,7 +125,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -187,9 +187,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hang" typeface="Malgun Gothic"/>
+        <a:font script="Hans" typeface="DengXian Light"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -222,9 +222,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hang" typeface="Malgun Gothic"/>
+        <a:font script="Hans" typeface="DengXian"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
